--- a/reports/telegram/aegis_usa_2026-09-01.xlsx
+++ b/reports/telegram/aegis_usa_2026-09-01.xlsx
@@ -1725,6 +1725,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -31444,6 +31445,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -31530,7 +31532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG38"/>
+  <dimension ref="A1:BG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -34992,12 +34994,12 @@
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>USA-R1-V-20260810-4d75a7</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
@@ -35007,17 +35009,17 @@
       </c>
       <c r="D17" s="30" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E17" s="30" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="F17" s="30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="G17" s="30" t="inlineStr">
@@ -35030,10 +35032,14 @@
       <c r="J17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="30" t="n"/>
-      <c r="L17" s="30" t="n"/>
+      <c r="K17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" s="30" t="n">
-        <v>86.5</v>
+        <v>79.3</v>
       </c>
       <c r="N17" s="30" t="inlineStr">
         <is>
@@ -35041,24 +35047,24 @@
         </is>
       </c>
       <c r="O17" s="30" t="n">
-        <v>52.9</v>
+        <v>56.1</v>
       </c>
       <c r="P17" s="30" t="n">
         <v>-0.8</v>
       </c>
       <c r="Q17" s="30" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="R17" s="30" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
         </is>
       </c>
       <c r="S17" s="30" t="n"/>
       <c r="T17" s="30" t="n">
-        <v>53.6</v>
+        <v>56.8</v>
       </c>
       <c r="U17" s="30" t="inlineStr">
         <is>
@@ -35066,55 +35072,57 @@
         </is>
       </c>
       <c r="V17" s="30" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="W17" s="30" t="n"/>
+        <v>29.2</v>
+      </c>
+      <c r="W17" s="30" t="n">
+        <v>4</v>
+      </c>
       <c r="X17" s="30" t="n">
         <v>0</v>
       </c>
       <c r="Y17" s="30" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="Z17" s="30" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="AA17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB17" s="30" t="n">
-        <v>368.54</v>
+        <v>382.45</v>
       </c>
       <c r="AC17" s="30" t="n">
-        <v>368.5400085449219</v>
+        <v>382.4500122070312</v>
       </c>
       <c r="AD17" s="30" t="n">
-        <v>351.39</v>
+        <v>365.29</v>
       </c>
       <c r="AE17" s="30" t="n">
-        <v>365.73</v>
+        <v>372.67</v>
       </c>
       <c r="AF17" s="30" t="n">
-        <v>340.632</v>
+        <v>346.84</v>
       </c>
       <c r="AG17" s="30" t="n">
-        <v>-7.57</v>
+        <v>-9.31</v>
       </c>
       <c r="AH17" s="30" t="n">
-        <v>387.2448000000001</v>
+        <v>413.26</v>
       </c>
       <c r="AI17" s="30" t="n">
-        <v>5.08</v>
+        <v>8.06</v>
       </c>
       <c r="AJ17" s="30" t="n">
-        <v>414.3519360000001</v>
+        <v>457.54</v>
       </c>
       <c r="AK17" s="30" t="n">
-        <v>12.43</v>
+        <v>19.63</v>
       </c>
       <c r="AL17" s="30" t="n">
-        <v>368.54</v>
+        <v>382.45</v>
       </c>
       <c r="AM17" s="30" t="n">
         <v>0</v>
@@ -35124,21 +35132,25 @@
       </c>
       <c r="AO17" s="30" t="n"/>
       <c r="AP17" s="30" t="n"/>
-      <c r="AQ17" s="30" t="n"/>
+      <c r="AQ17" s="30" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
       <c r="AR17" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="AS17" s="30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT17" s="30" t="n">
-        <v>5.08</v>
+        <v>8.06</v>
       </c>
       <c r="AU17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:27</t>
+          <t>2026-08-11 04:16</t>
         </is>
       </c>
       <c r="AV17" s="30" t="inlineStr">
@@ -35180,12 +35192,12 @@
       </c>
       <c r="BE17" s="30" t="inlineStr">
         <is>
-          <t>Trailing Stop @ 340.63</t>
+          <t>Trailing Stop @ 346.84</t>
         </is>
       </c>
       <c r="BF17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="BG17" s="30" t="inlineStr">
@@ -35195,4383 +35207,213 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-TRV-20260810-6f873c</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>USA-R2-V-20260810-69160d</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E18" s="30" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="F18" s="30" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="G18" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H18" s="30" t="n"/>
-      <c r="I18" s="30" t="n"/>
-      <c r="J18" s="30" t="n">
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="n"/>
+      <c r="I18" s="31" t="n"/>
+      <c r="J18" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="30" t="n"/>
-      <c r="M18" s="30" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="N18" s="30" t="inlineStr">
+      <c r="K18" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="31" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N18" s="31" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O18" s="30" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="P18" s="30" t="n">
+      <c r="O18" s="31" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P18" s="31" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q18" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R18" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S18" s="30" t="n"/>
-      <c r="T18" s="30" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U18" s="30" t="inlineStr">
+      <c r="Q18" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R18" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S18" s="31" t="n"/>
+      <c r="T18" s="31" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U18" s="31" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V18" s="30" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="W18" s="30" t="n"/>
-      <c r="X18" s="30" t="n">
+      <c r="V18" s="31" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W18" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="X18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="Y18" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z18" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA18" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB18" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AC18" s="30" t="n">
-        <v>382.4500122070312</v>
-      </c>
-      <c r="AD18" s="30" t="n">
-        <v>365.29</v>
-      </c>
-      <c r="AE18" s="30" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AF18" s="30" t="n">
-        <v>350.531</v>
-      </c>
-      <c r="AG18" s="30" t="n">
-        <v>-8.35</v>
-      </c>
-      <c r="AH18" s="30" t="n">
-        <v>413.26</v>
-      </c>
-      <c r="AI18" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AJ18" s="30" t="n">
-        <v>442.1882</v>
-      </c>
-      <c r="AK18" s="30" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="AL18" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AM18" s="30" t="n">
+      <c r="Y18" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z18" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA18" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB18" s="31" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AC18" s="31" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="AD18" s="31" t="n">
+        <v>364.85</v>
+      </c>
+      <c r="AE18" s="31" t="n">
+        <v>372.23</v>
+      </c>
+      <c r="AF18" s="31" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="AG18" s="31" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH18" s="31" t="n">
+        <v>398.02</v>
+      </c>
+      <c r="AI18" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ18" s="31" t="n">
+        <v>423.82</v>
+      </c>
+      <c r="AK18" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL18" s="31" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AM18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="AN18" s="30" t="n">
+      <c r="AN18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="AO18" s="30" t="n"/>
-      <c r="AP18" s="30" t="n"/>
-      <c r="AQ18" s="30" t="n"/>
-      <c r="AR18" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS18" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT18" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AU18" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV18" s="30" t="inlineStr">
+      <c r="AO18" s="31" t="n"/>
+      <c r="AP18" s="31" t="n"/>
+      <c r="AQ18" s="31" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Quality</t>
+        </is>
+      </c>
+      <c r="AR18" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS18" s="31" t="n"/>
+      <c r="AT18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV18" s="31" t="inlineStr">
         <is>
           <t>LargeCap (S&amp;P 500)</t>
         </is>
       </c>
-      <c r="AW18" s="30" t="inlineStr">
+      <c r="AW18" s="31" t="inlineStr">
         <is>
           <t>🆕 NEW</t>
         </is>
       </c>
-      <c r="AX18" s="30" t="n"/>
-      <c r="AY18" s="30" t="inlineStr"/>
-      <c r="AZ18" s="30" t="inlineStr">
+      <c r="AX18" s="31" t="n"/>
+      <c r="AY18" s="31" t="inlineStr"/>
+      <c r="AZ18" s="31" t="inlineStr">
         <is>
           <t>🟠 PROTECT</t>
         </is>
       </c>
-      <c r="BA18" s="30" t="inlineStr">
+      <c r="BA18" s="31" t="inlineStr">
         <is>
           <t>🟡 MEDIUM</t>
         </is>
       </c>
-      <c r="BB18" s="30" t="inlineStr">
+      <c r="BB18" s="31" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="BC18" s="30" t="inlineStr">
+      <c r="BC18" s="31" t="inlineStr">
         <is>
           <t>TIGHTEN STOP</t>
         </is>
       </c>
-      <c r="BD18" s="30" t="inlineStr">
+      <c r="BD18" s="31" t="inlineStr">
         <is>
           <t>TOMORROW</t>
         </is>
       </c>
-      <c r="BE18" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 350.53</t>
-        </is>
-      </c>
-      <c r="BF18" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG18" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-NVDA-20260810-2aa027</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D19" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E19" s="30" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="F19" s="30" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="G19" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H19" s="30" t="n"/>
-      <c r="I19" s="30" t="n"/>
-      <c r="J19" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="30" t="n"/>
-      <c r="L19" s="30" t="n"/>
-      <c r="M19" s="30" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="N19" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O19" s="30" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="P19" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q19" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R19" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S19" s="30" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T19" s="30" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U19" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V19" s="30" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="W19" s="30" t="n"/>
-      <c r="X19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z19" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA19" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB19" s="30" t="n">
-        <v>219.22</v>
-      </c>
-      <c r="AC19" s="30" t="n">
-        <v>219.2200012207031</v>
-      </c>
-      <c r="AD19" s="30" t="n">
-        <v>198.75</v>
-      </c>
-      <c r="AE19" s="30" t="n">
-        <v>206.87</v>
-      </c>
-      <c r="AF19" s="30" t="n">
-        <v>192.6695</v>
-      </c>
-      <c r="AG19" s="30" t="n">
-        <v>-12.11</v>
-      </c>
-      <c r="AH19" s="30" t="n">
-        <v>219.0348</v>
-      </c>
-      <c r="AI19" s="30" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ19" s="30" t="n">
-        <v>234.367236</v>
-      </c>
-      <c r="AK19" s="30" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="AL19" s="30" t="n">
-        <v>219.22</v>
-      </c>
-      <c r="AM19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="30" t="n"/>
-      <c r="AP19" s="30" t="n"/>
-      <c r="AQ19" s="30" t="n"/>
-      <c r="AR19" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS19" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT19" s="30" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AU19" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV19" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW19" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX19" s="30" t="n"/>
-      <c r="AY19" s="30" t="inlineStr"/>
-      <c r="AZ19" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA19" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB19" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC19" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD19" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE19" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 192.67</t>
-        </is>
-      </c>
-      <c r="BF19" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG19" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
-        </is>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C20" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D20" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E20" s="30" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="F20" s="30" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="G20" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H20" s="30" t="n"/>
-      <c r="I20" s="30" t="n"/>
-      <c r="J20" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" s="30" t="n"/>
-      <c r="L20" s="30" t="n"/>
-      <c r="M20" s="30" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="N20" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O20" s="30" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P20" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q20" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R20" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S20" s="30" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T20" s="30" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U20" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V20" s="30" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="W20" s="30" t="n"/>
-      <c r="X20" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z20" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA20" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB20" s="30" t="n">
-        <v>487.46</v>
-      </c>
-      <c r="AC20" s="30" t="n">
-        <v>487.4599914550781</v>
-      </c>
-      <c r="AD20" s="30" t="n">
-        <v>385.94</v>
-      </c>
-      <c r="AE20" s="30" t="n">
-        <v>401.7</v>
-      </c>
-      <c r="AF20" s="30" t="n">
-        <v>374.129</v>
-      </c>
-      <c r="AG20" s="30" t="n">
-        <v>-23.25</v>
-      </c>
-      <c r="AH20" s="30" t="n">
-        <v>425.3256</v>
-      </c>
-      <c r="AI20" s="30" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="AJ20" s="30" t="n">
-        <v>455.098392</v>
-      </c>
-      <c r="AK20" s="30" t="n">
-        <v>-6.64</v>
-      </c>
-      <c r="AL20" s="30" t="n">
-        <v>487.46</v>
-      </c>
-      <c r="AM20" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="30" t="n"/>
-      <c r="AP20" s="30" t="n"/>
-      <c r="AQ20" s="30" t="n"/>
-      <c r="AR20" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS20" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT20" s="30" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="AU20" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV20" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW20" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX20" s="30" t="n"/>
-      <c r="AY20" s="30" t="inlineStr"/>
-      <c r="AZ20" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA20" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB20" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC20" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD20" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE20" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 374.13</t>
-        </is>
-      </c>
-      <c r="BF20" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG20" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-KO-20260810-af15a9</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="F21" s="31" t="inlineStr">
-        <is>
-          <t>Coca-Cola</t>
-        </is>
-      </c>
-      <c r="G21" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H21" s="31" t="n"/>
-      <c r="I21" s="31" t="n"/>
-      <c r="J21" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" s="31" t="n"/>
-      <c r="L21" s="31" t="n"/>
-      <c r="M21" s="31" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="N21" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O21" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P21" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q21" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R21" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S21" s="31" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T21" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U21" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V21" s="31" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="W21" s="31" t="n"/>
-      <c r="X21" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z21" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA21" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB21" s="31" t="n">
-        <v>86.83</v>
-      </c>
-      <c r="AC21" s="31" t="n">
-        <v>86.83000183105469</v>
-      </c>
-      <c r="AD21" s="31" t="n">
-        <v>79.93000000000001</v>
-      </c>
-      <c r="AE21" s="31" t="n">
-        <v>83.19</v>
-      </c>
-      <c r="AF21" s="31" t="n">
-        <v>77.482</v>
-      </c>
-      <c r="AG21" s="31" t="n">
-        <v>-10.77</v>
-      </c>
-      <c r="AH21" s="31" t="n">
-        <v>88.0848</v>
-      </c>
-      <c r="AI21" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ21" s="31" t="n">
-        <v>94.250736</v>
-      </c>
-      <c r="AK21" s="31" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="AL21" s="31" t="n">
-        <v>86.83</v>
-      </c>
-      <c r="AM21" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="31" t="n"/>
-      <c r="AP21" s="31" t="n"/>
-      <c r="AQ21" s="31" t="n"/>
-      <c r="AR21" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS21" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT21" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AU21" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV21" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW21" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX21" s="31" t="n"/>
-      <c r="AY21" s="31" t="inlineStr"/>
-      <c r="AZ21" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA21" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB21" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC21" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD21" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE21" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 77.48</t>
-        </is>
-      </c>
-      <c r="BF21" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG21" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-HON-20260810-0b8118</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D22" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="F22" s="31" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="G22" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="31" t="n"/>
-      <c r="M22" s="31" t="n">
-        <v>76</v>
-      </c>
-      <c r="N22" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O22" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P22" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q22" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R22" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S22" s="31" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T22" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U22" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V22" s="31" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="W22" s="31" t="n"/>
-      <c r="X22" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z22" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA22" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB22" s="31" t="n">
-        <v>248.12</v>
-      </c>
-      <c r="AC22" s="31" t="n">
-        <v>248.1199951171875</v>
-      </c>
-      <c r="AD22" s="31" t="n">
-        <v>220.52</v>
-      </c>
-      <c r="AE22" s="31" t="n">
-        <v>229.52</v>
-      </c>
-      <c r="AF22" s="31" t="n">
-        <v>213.769</v>
-      </c>
-      <c r="AG22" s="31" t="n">
-        <v>-13.84</v>
-      </c>
-      <c r="AH22" s="31" t="n">
-        <v>243.0216</v>
-      </c>
-      <c r="AI22" s="31" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="AJ22" s="31" t="n">
-        <v>260.0331120000001</v>
-      </c>
-      <c r="AK22" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AL22" s="31" t="n">
-        <v>248.12</v>
-      </c>
-      <c r="AM22" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="31" t="n"/>
-      <c r="AP22" s="31" t="n"/>
-      <c r="AQ22" s="31" t="n"/>
-      <c r="AR22" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS22" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT22" s="31" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="AU22" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV22" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW22" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX22" s="31" t="n"/>
-      <c r="AY22" s="31" t="inlineStr"/>
-      <c r="AZ22" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA22" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB22" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC22" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD22" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE22" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 213.77</t>
-        </is>
-      </c>
-      <c r="BF22" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG22" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-AAPL-20260810-d82b13</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="F23" s="31" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="G23" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="31" t="n"/>
-      <c r="J23" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="31" t="n"/>
-      <c r="M23" s="31" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="N23" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O23" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P23" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q23" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R23" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U23" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V23" s="31" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="W23" s="31" t="n"/>
-      <c r="X23" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z23" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA23" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB23" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AC23" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AD23" s="31" t="n">
-        <v>327.07</v>
-      </c>
-      <c r="AE23" s="31" t="n">
-        <v>340.41</v>
-      </c>
-      <c r="AF23" s="31" t="n">
-        <v>317.053</v>
-      </c>
-      <c r="AG23" s="31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH23" s="31" t="n">
-        <v>360.4392</v>
-      </c>
-      <c r="AI23" s="31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AJ23" s="31" t="n">
-        <v>385.669944</v>
-      </c>
-      <c r="AK23" s="31" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="AL23" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AM23" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="31" t="n"/>
-      <c r="AP23" s="31" t="n"/>
-      <c r="AQ23" s="31" t="n"/>
-      <c r="AR23" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS23" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT23" s="31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AU23" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV23" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW23" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX23" s="31" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="AY23" s="31" t="inlineStr">
-        <is>
-          <t>🏆 QUALITY</t>
-        </is>
-      </c>
-      <c r="AZ23" s="31" t="inlineStr">
-        <is>
-          <t>🟢 HOLD</t>
-        </is>
-      </c>
-      <c r="BA23" s="31" t="inlineStr">
-        <is>
-          <t>🟢 LOW</t>
-        </is>
-      </c>
-      <c r="BB23" s="31" t="inlineStr">
-        <is>
-          <t>Compounder</t>
-        </is>
-      </c>
-      <c r="BC23" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="BD23" s="31" t="inlineStr">
-        <is>
-          <t>30 DAYS</t>
-        </is>
-      </c>
-      <c r="BE23" s="31" t="inlineStr">
-        <is>
-          <t>Watching @ 360.44</t>
-        </is>
-      </c>
-      <c r="BF23" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="BG23" s="31" t="inlineStr">
-        <is>
-          <t>⚪ No immediate execution</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-JPM-20260810-a6a394</t>
-        </is>
-      </c>
-      <c r="B24" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D24" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="F24" s="31" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase</t>
-        </is>
-      </c>
-      <c r="G24" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="N24" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O24" s="31" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="P24" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q24" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R24" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S24" s="31" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T24" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="U24" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V24" s="31" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="W24" s="31" t="n"/>
-      <c r="X24" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z24" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA24" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB24" s="31" t="n">
-        <v>359.24</v>
-      </c>
-      <c r="AC24" s="31" t="n">
-        <v>359.239990234375</v>
-      </c>
-      <c r="AD24" s="31" t="n">
-        <v>334.28</v>
-      </c>
-      <c r="AE24" s="31" t="n">
-        <v>347.92</v>
-      </c>
-      <c r="AF24" s="31" t="n">
-        <v>324.045</v>
-      </c>
-      <c r="AG24" s="31" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="AH24" s="31" t="n">
-        <v>368.388</v>
-      </c>
-      <c r="AI24" s="31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AJ24" s="31" t="n">
-        <v>394.1751600000001</v>
-      </c>
-      <c r="AK24" s="31" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="AL24" s="31" t="n">
-        <v>359.24</v>
-      </c>
-      <c r="AM24" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="31" t="n"/>
-      <c r="AP24" s="31" t="n"/>
-      <c r="AQ24" s="31" t="n"/>
-      <c r="AR24" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS24" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT24" s="31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU24" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV24" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW24" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX24" s="31" t="n"/>
-      <c r="AY24" s="31" t="inlineStr"/>
-      <c r="AZ24" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA24" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB24" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC24" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD24" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE24" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 324.05</t>
-        </is>
-      </c>
-      <c r="BF24" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG24" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-GS-20260810-c6e885</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="F25" s="31" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="G25" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="31" t="n"/>
-      <c r="J25" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="N25" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O25" s="31" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="P25" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q25" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R25" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="U25" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V25" s="31" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="W25" s="31" t="n"/>
-      <c r="X25" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z25" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA25" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB25" s="31" t="n">
-        <v>1060.38</v>
-      </c>
-      <c r="AC25" s="31" t="n">
-        <v>1060.380004882812</v>
-      </c>
-      <c r="AD25" s="31" t="n">
-        <v>1043.92</v>
-      </c>
-      <c r="AE25" s="31" t="n">
-        <v>1086.52</v>
-      </c>
-      <c r="AF25" s="31" t="n">
-        <v>1011.959</v>
-      </c>
-      <c r="AG25" s="31" t="n">
-        <v>-4.57</v>
-      </c>
-      <c r="AH25" s="31" t="n">
-        <v>1150.4376</v>
-      </c>
-      <c r="AI25" s="31" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="AJ25" s="31" t="n">
-        <v>1230.968232</v>
-      </c>
-      <c r="AK25" s="31" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="AL25" s="31" t="n">
-        <v>1060.38</v>
-      </c>
-      <c r="AM25" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="31" t="n"/>
-      <c r="AP25" s="31" t="n"/>
-      <c r="AQ25" s="31" t="n"/>
-      <c r="AR25" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS25" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT25" s="31" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="AU25" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV25" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW25" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX25" s="31" t="n"/>
-      <c r="AY25" s="31" t="inlineStr"/>
-      <c r="AZ25" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA25" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB25" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC25" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD25" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE25" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 1011.96</t>
-        </is>
-      </c>
-      <c r="BF25" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG25" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-MMM-20260810-0649c0</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D26" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>MMM</t>
-        </is>
-      </c>
-      <c r="F26" s="31" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="G26" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-      <c r="J26" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="K26" s="31" t="n"/>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="31" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="N26" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O26" s="31" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P26" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q26" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R26" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S26" s="31" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T26" s="31" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U26" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V26" s="31" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="W26" s="31" t="n"/>
-      <c r="X26" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z26" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA26" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB26" s="31" t="n">
-        <v>182.08</v>
-      </c>
-      <c r="AC26" s="31" t="n">
-        <v>182.0800018310547</v>
-      </c>
-      <c r="AD26" s="31" t="n">
-        <v>156.64</v>
-      </c>
-      <c r="AE26" s="31" t="n">
-        <v>163.04</v>
-      </c>
-      <c r="AF26" s="31" t="n">
-        <v>151.848</v>
-      </c>
-      <c r="AG26" s="31" t="n">
-        <v>-16.6</v>
-      </c>
-      <c r="AH26" s="31" t="n">
-        <v>172.6272</v>
-      </c>
-      <c r="AI26" s="31" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="AJ26" s="31" t="n">
-        <v>184.711104</v>
-      </c>
-      <c r="AK26" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL26" s="31" t="n">
-        <v>182.08</v>
-      </c>
-      <c r="AM26" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="31" t="n"/>
-      <c r="AP26" s="31" t="n"/>
-      <c r="AQ26" s="31" t="n"/>
-      <c r="AR26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS26" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT26" s="31" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="AU26" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV26" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW26" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX26" s="31" t="n"/>
-      <c r="AY26" s="31" t="inlineStr"/>
-      <c r="AZ26" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA26" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB26" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC26" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD26" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE26" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 151.85</t>
-        </is>
-      </c>
-      <c r="BF26" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG26" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>USA-R2-TRV-20260810-9cd25d</t>
-        </is>
-      </c>
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C27" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D27" s="30" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E27" s="30" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="F27" s="30" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="G27" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H27" s="30" t="n"/>
-      <c r="I27" s="30" t="n"/>
-      <c r="J27" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="30" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="N27" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O27" s="30" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="P27" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q27" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R27" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S27" s="30" t="n"/>
-      <c r="T27" s="30" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U27" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V27" s="30" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="W27" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="X27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="30" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z27" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA27" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB27" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AC27" s="30" t="n">
-        <v>382.4500122070312</v>
-      </c>
-      <c r="AD27" s="30" t="n">
-        <v>365.29</v>
-      </c>
-      <c r="AE27" s="30" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AF27" s="30" t="n">
-        <v>346.84</v>
-      </c>
-      <c r="AG27" s="30" t="n">
-        <v>-9.31</v>
-      </c>
-      <c r="AH27" s="30" t="n">
-        <v>413.26</v>
-      </c>
-      <c r="AI27" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AJ27" s="30" t="n">
-        <v>457.54</v>
-      </c>
-      <c r="AK27" s="30" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="AL27" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AM27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="30" t="n"/>
-      <c r="AP27" s="30" t="n"/>
-      <c r="AQ27" s="30" t="inlineStr">
-        <is>
-          <t>Momentum · Value · Trend</t>
-        </is>
-      </c>
-      <c r="AR27" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS27" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT27" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AU27" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV27" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW27" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX27" s="30" t="n"/>
-      <c r="AY27" s="30" t="inlineStr"/>
-      <c r="AZ27" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA27" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB27" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC27" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD27" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE27" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 346.84</t>
-        </is>
-      </c>
-      <c r="BF27" s="30" t="inlineStr">
+      <c r="BE18" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 350.11</t>
+        </is>
+      </c>
+      <c r="BF18" s="31" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="BG27" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>USA-R2-V-20260810-69160d</t>
-        </is>
-      </c>
-      <c r="B28" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E28" s="31" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F28" s="31" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="G28" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="31" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="N28" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O28" s="31" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P28" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q28" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R28" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S28" s="31" t="n"/>
-      <c r="T28" s="31" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U28" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V28" s="31" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W28" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="X28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z28" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA28" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB28" s="31" t="n">
-        <v>368.54</v>
-      </c>
-      <c r="AC28" s="31" t="n">
-        <v>368.5400085449219</v>
-      </c>
-      <c r="AD28" s="31" t="n">
-        <v>364.85</v>
-      </c>
-      <c r="AE28" s="31" t="n">
-        <v>372.23</v>
-      </c>
-      <c r="AF28" s="31" t="n">
-        <v>350.11</v>
-      </c>
-      <c r="AG28" s="31" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH28" s="31" t="n">
-        <v>398.02</v>
-      </c>
-      <c r="AI28" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" s="31" t="n">
-        <v>423.82</v>
-      </c>
-      <c r="AK28" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL28" s="31" t="n">
-        <v>368.54</v>
-      </c>
-      <c r="AM28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="31" t="n"/>
-      <c r="AP28" s="31" t="n"/>
-      <c r="AQ28" s="31" t="inlineStr">
-        <is>
-          <t>Momentum · Trend · Quality</t>
-        </is>
-      </c>
-      <c r="AR28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS28" s="31" t="n"/>
-      <c r="AT28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV28" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW28" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX28" s="31" t="n"/>
-      <c r="AY28" s="31" t="inlineStr"/>
-      <c r="AZ28" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA28" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB28" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC28" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD28" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE28" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 350.11</t>
-        </is>
-      </c>
-      <c r="BF28" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG28" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-V-20260810-4d75a7</t>
-        </is>
-      </c>
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C29" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D29" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E29" s="30" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F29" s="30" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="G29" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H29" s="30" t="n"/>
-      <c r="I29" s="30" t="n"/>
-      <c r="J29" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="30" t="n"/>
-      <c r="L29" s="30" t="n"/>
-      <c r="M29" s="30" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="N29" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O29" s="30" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P29" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q29" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R29" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S29" s="30" t="n"/>
-      <c r="T29" s="30" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U29" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V29" s="30" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="W29" s="30" t="n"/>
-      <c r="X29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z29" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA29" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB29" s="30" t="n">
-        <v>368.54</v>
-      </c>
-      <c r="AC29" s="30" t="n">
-        <v>368.5400085449219</v>
-      </c>
-      <c r="AD29" s="30" t="n">
-        <v>351.39</v>
-      </c>
-      <c r="AE29" s="30" t="n">
-        <v>365.73</v>
-      </c>
-      <c r="AF29" s="30" t="n">
-        <v>340.632</v>
-      </c>
-      <c r="AG29" s="30" t="n">
-        <v>-7.57</v>
-      </c>
-      <c r="AH29" s="30" t="n">
-        <v>387.2448000000001</v>
-      </c>
-      <c r="AI29" s="30" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="AJ29" s="30" t="n">
-        <v>414.3519360000001</v>
-      </c>
-      <c r="AK29" s="30" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="AL29" s="30" t="n">
-        <v>368.54</v>
-      </c>
-      <c r="AM29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="30" t="n"/>
-      <c r="AP29" s="30" t="n"/>
-      <c r="AQ29" s="30" t="n"/>
-      <c r="AR29" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS29" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT29" s="30" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="AU29" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV29" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW29" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX29" s="30" t="n"/>
-      <c r="AY29" s="30" t="inlineStr"/>
-      <c r="AZ29" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA29" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB29" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC29" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD29" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE29" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 340.63</t>
-        </is>
-      </c>
-      <c r="BF29" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG29" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-TRV-20260810-6f873c</t>
-        </is>
-      </c>
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C30" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E30" s="30" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="F30" s="30" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="G30" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H30" s="30" t="n"/>
-      <c r="I30" s="30" t="n"/>
-      <c r="J30" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="30" t="n"/>
-      <c r="L30" s="30" t="n"/>
-      <c r="M30" s="30" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="N30" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O30" s="30" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="P30" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q30" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R30" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S30" s="30" t="n"/>
-      <c r="T30" s="30" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U30" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V30" s="30" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="W30" s="30" t="n"/>
-      <c r="X30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z30" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA30" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB30" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AC30" s="30" t="n">
-        <v>382.4500122070312</v>
-      </c>
-      <c r="AD30" s="30" t="n">
-        <v>365.29</v>
-      </c>
-      <c r="AE30" s="30" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AF30" s="30" t="n">
-        <v>350.531</v>
-      </c>
-      <c r="AG30" s="30" t="n">
-        <v>-8.35</v>
-      </c>
-      <c r="AH30" s="30" t="n">
-        <v>413.26</v>
-      </c>
-      <c r="AI30" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AJ30" s="30" t="n">
-        <v>442.1882</v>
-      </c>
-      <c r="AK30" s="30" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="AL30" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AM30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="30" t="n"/>
-      <c r="AP30" s="30" t="n"/>
-      <c r="AQ30" s="30" t="n"/>
-      <c r="AR30" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS30" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT30" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AU30" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV30" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW30" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX30" s="30" t="n"/>
-      <c r="AY30" s="30" t="inlineStr"/>
-      <c r="AZ30" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA30" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB30" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC30" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD30" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE30" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 350.53</t>
-        </is>
-      </c>
-      <c r="BF30" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG30" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-NVDA-20260810-2aa027</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E31" s="30" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="F31" s="30" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="G31" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H31" s="30" t="n"/>
-      <c r="I31" s="30" t="n"/>
-      <c r="J31" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" s="30" t="n"/>
-      <c r="L31" s="30" t="n"/>
-      <c r="M31" s="30" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="N31" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O31" s="30" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="P31" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q31" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R31" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S31" s="30" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T31" s="30" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U31" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V31" s="30" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="W31" s="30" t="n"/>
-      <c r="X31" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z31" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA31" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB31" s="30" t="n">
-        <v>219.22</v>
-      </c>
-      <c r="AC31" s="30" t="n">
-        <v>219.2200012207031</v>
-      </c>
-      <c r="AD31" s="30" t="n">
-        <v>198.75</v>
-      </c>
-      <c r="AE31" s="30" t="n">
-        <v>206.87</v>
-      </c>
-      <c r="AF31" s="30" t="n">
-        <v>192.6695</v>
-      </c>
-      <c r="AG31" s="30" t="n">
-        <v>-12.11</v>
-      </c>
-      <c r="AH31" s="30" t="n">
-        <v>219.0348</v>
-      </c>
-      <c r="AI31" s="30" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ31" s="30" t="n">
-        <v>234.367236</v>
-      </c>
-      <c r="AK31" s="30" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="AL31" s="30" t="n">
-        <v>219.22</v>
-      </c>
-      <c r="AM31" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="30" t="n"/>
-      <c r="AP31" s="30" t="n"/>
-      <c r="AQ31" s="30" t="n"/>
-      <c r="AR31" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS31" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT31" s="30" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AU31" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV31" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW31" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX31" s="30" t="n"/>
-      <c r="AY31" s="30" t="inlineStr"/>
-      <c r="AZ31" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA31" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB31" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC31" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD31" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE31" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 192.67</t>
-        </is>
-      </c>
-      <c r="BF31" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG31" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C32" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D32" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E32" s="30" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="F32" s="30" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="G32" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H32" s="30" t="n"/>
-      <c r="I32" s="30" t="n"/>
-      <c r="J32" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="K32" s="30" t="n"/>
-      <c r="L32" s="30" t="n"/>
-      <c r="M32" s="30" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="N32" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O32" s="30" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P32" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q32" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R32" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S32" s="30" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T32" s="30" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U32" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V32" s="30" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="W32" s="30" t="n"/>
-      <c r="X32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z32" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA32" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB32" s="30" t="n">
-        <v>487.46</v>
-      </c>
-      <c r="AC32" s="30" t="n">
-        <v>487.4599914550781</v>
-      </c>
-      <c r="AD32" s="30" t="n">
-        <v>385.94</v>
-      </c>
-      <c r="AE32" s="30" t="n">
-        <v>401.7</v>
-      </c>
-      <c r="AF32" s="30" t="n">
-        <v>374.129</v>
-      </c>
-      <c r="AG32" s="30" t="n">
-        <v>-23.25</v>
-      </c>
-      <c r="AH32" s="30" t="n">
-        <v>425.3256</v>
-      </c>
-      <c r="AI32" s="30" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="AJ32" s="30" t="n">
-        <v>455.098392</v>
-      </c>
-      <c r="AK32" s="30" t="n">
-        <v>-6.64</v>
-      </c>
-      <c r="AL32" s="30" t="n">
-        <v>487.46</v>
-      </c>
-      <c r="AM32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="30" t="n"/>
-      <c r="AP32" s="30" t="n"/>
-      <c r="AQ32" s="30" t="n"/>
-      <c r="AR32" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS32" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT32" s="30" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="AU32" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV32" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW32" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX32" s="30" t="n"/>
-      <c r="AY32" s="30" t="inlineStr"/>
-      <c r="AZ32" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA32" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB32" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC32" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD32" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE32" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 374.13</t>
-        </is>
-      </c>
-      <c r="BF32" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG32" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-KO-20260810-af15a9</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="F33" s="31" t="inlineStr">
-        <is>
-          <t>Coca-Cola</t>
-        </is>
-      </c>
-      <c r="G33" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="31" t="n"/>
-      <c r="M33" s="31" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="N33" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O33" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P33" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q33" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R33" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S33" s="31" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T33" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U33" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V33" s="31" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="W33" s="31" t="n"/>
-      <c r="X33" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z33" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA33" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB33" s="31" t="n">
-        <v>86.83</v>
-      </c>
-      <c r="AC33" s="31" t="n">
-        <v>86.83000183105469</v>
-      </c>
-      <c r="AD33" s="31" t="n">
-        <v>79.93000000000001</v>
-      </c>
-      <c r="AE33" s="31" t="n">
-        <v>83.19</v>
-      </c>
-      <c r="AF33" s="31" t="n">
-        <v>77.482</v>
-      </c>
-      <c r="AG33" s="31" t="n">
-        <v>-10.77</v>
-      </c>
-      <c r="AH33" s="31" t="n">
-        <v>88.0848</v>
-      </c>
-      <c r="AI33" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ33" s="31" t="n">
-        <v>94.250736</v>
-      </c>
-      <c r="AK33" s="31" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="AL33" s="31" t="n">
-        <v>86.83</v>
-      </c>
-      <c r="AM33" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="31" t="n"/>
-      <c r="AP33" s="31" t="n"/>
-      <c r="AQ33" s="31" t="n"/>
-      <c r="AR33" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS33" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT33" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AU33" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV33" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW33" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX33" s="31" t="n"/>
-      <c r="AY33" s="31" t="inlineStr"/>
-      <c r="AZ33" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA33" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB33" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC33" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD33" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE33" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 77.48</t>
-        </is>
-      </c>
-      <c r="BF33" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG33" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-HON-20260810-0b8118</t>
-        </is>
-      </c>
-      <c r="B34" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D34" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="F34" s="31" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="G34" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n">
-        <v>76</v>
-      </c>
-      <c r="N34" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O34" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P34" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q34" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R34" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S34" s="31" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T34" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U34" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V34" s="31" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="W34" s="31" t="n"/>
-      <c r="X34" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z34" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA34" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB34" s="31" t="n">
-        <v>248.12</v>
-      </c>
-      <c r="AC34" s="31" t="n">
-        <v>248.1199951171875</v>
-      </c>
-      <c r="AD34" s="31" t="n">
-        <v>220.52</v>
-      </c>
-      <c r="AE34" s="31" t="n">
-        <v>229.52</v>
-      </c>
-      <c r="AF34" s="31" t="n">
-        <v>213.769</v>
-      </c>
-      <c r="AG34" s="31" t="n">
-        <v>-13.84</v>
-      </c>
-      <c r="AH34" s="31" t="n">
-        <v>243.0216</v>
-      </c>
-      <c r="AI34" s="31" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="AJ34" s="31" t="n">
-        <v>260.0331120000001</v>
-      </c>
-      <c r="AK34" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AL34" s="31" t="n">
-        <v>248.12</v>
-      </c>
-      <c r="AM34" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="31" t="n"/>
-      <c r="AP34" s="31" t="n"/>
-      <c r="AQ34" s="31" t="n"/>
-      <c r="AR34" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS34" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT34" s="31" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="AU34" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV34" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW34" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX34" s="31" t="n"/>
-      <c r="AY34" s="31" t="inlineStr"/>
-      <c r="AZ34" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA34" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB34" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC34" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD34" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE34" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 213.77</t>
-        </is>
-      </c>
-      <c r="BF34" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG34" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-AAPL-20260810-d82b13</t>
-        </is>
-      </c>
-      <c r="B35" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C35" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="F35" s="31" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="G35" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="N35" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O35" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P35" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q35" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R35" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U35" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V35" s="31" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="W35" s="31" t="n"/>
-      <c r="X35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z35" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA35" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB35" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AC35" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AD35" s="31" t="n">
-        <v>327.07</v>
-      </c>
-      <c r="AE35" s="31" t="n">
-        <v>340.41</v>
-      </c>
-      <c r="AF35" s="31" t="n">
-        <v>317.053</v>
-      </c>
-      <c r="AG35" s="31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH35" s="31" t="n">
-        <v>360.4392</v>
-      </c>
-      <c r="AI35" s="31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AJ35" s="31" t="n">
-        <v>385.669944</v>
-      </c>
-      <c r="AK35" s="31" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="AL35" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AM35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="31" t="n"/>
-      <c r="AP35" s="31" t="n"/>
-      <c r="AQ35" s="31" t="n"/>
-      <c r="AR35" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS35" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT35" s="31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AU35" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV35" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW35" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX35" s="31" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="AY35" s="31" t="inlineStr">
-        <is>
-          <t>🏆 QUALITY</t>
-        </is>
-      </c>
-      <c r="AZ35" s="31" t="inlineStr">
-        <is>
-          <t>🟢 HOLD</t>
-        </is>
-      </c>
-      <c r="BA35" s="31" t="inlineStr">
-        <is>
-          <t>🟢 LOW</t>
-        </is>
-      </c>
-      <c r="BB35" s="31" t="inlineStr">
-        <is>
-          <t>Compounder</t>
-        </is>
-      </c>
-      <c r="BC35" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="BD35" s="31" t="inlineStr">
-        <is>
-          <t>30 DAYS</t>
-        </is>
-      </c>
-      <c r="BE35" s="31" t="inlineStr">
-        <is>
-          <t>Watching @ 360.44</t>
-        </is>
-      </c>
-      <c r="BF35" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="BG35" s="31" t="inlineStr">
-        <is>
-          <t>⚪ No immediate execution</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-JPM-20260810-a6a394</t>
-        </is>
-      </c>
-      <c r="B36" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C36" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D36" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E36" s="31" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="F36" s="31" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase</t>
-        </is>
-      </c>
-      <c r="G36" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="N36" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O36" s="31" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="P36" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q36" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R36" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S36" s="31" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T36" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="U36" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V36" s="31" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="W36" s="31" t="n"/>
-      <c r="X36" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z36" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA36" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB36" s="31" t="n">
-        <v>359.24</v>
-      </c>
-      <c r="AC36" s="31" t="n">
-        <v>359.239990234375</v>
-      </c>
-      <c r="AD36" s="31" t="n">
-        <v>334.28</v>
-      </c>
-      <c r="AE36" s="31" t="n">
-        <v>347.92</v>
-      </c>
-      <c r="AF36" s="31" t="n">
-        <v>324.045</v>
-      </c>
-      <c r="AG36" s="31" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="AH36" s="31" t="n">
-        <v>368.388</v>
-      </c>
-      <c r="AI36" s="31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AJ36" s="31" t="n">
-        <v>394.1751600000001</v>
-      </c>
-      <c r="AK36" s="31" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="AL36" s="31" t="n">
-        <v>359.24</v>
-      </c>
-      <c r="AM36" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" s="31" t="n"/>
-      <c r="AP36" s="31" t="n"/>
-      <c r="AQ36" s="31" t="n"/>
-      <c r="AR36" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS36" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT36" s="31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU36" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV36" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW36" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX36" s="31" t="n"/>
-      <c r="AY36" s="31" t="inlineStr"/>
-      <c r="AZ36" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA36" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB36" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC36" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD36" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE36" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 324.05</t>
-        </is>
-      </c>
-      <c r="BF36" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG36" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-GS-20260810-c6e885</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="F37" s="31" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="G37" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H37" s="31" t="n"/>
-      <c r="I37" s="31" t="n"/>
-      <c r="J37" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" s="31" t="n"/>
-      <c r="L37" s="31" t="n"/>
-      <c r="M37" s="31" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="N37" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O37" s="31" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="P37" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q37" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R37" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S37" s="31" t="n"/>
-      <c r="T37" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="U37" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V37" s="31" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="W37" s="31" t="n"/>
-      <c r="X37" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z37" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA37" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB37" s="31" t="n">
-        <v>1060.38</v>
-      </c>
-      <c r="AC37" s="31" t="n">
-        <v>1060.380004882812</v>
-      </c>
-      <c r="AD37" s="31" t="n">
-        <v>1043.92</v>
-      </c>
-      <c r="AE37" s="31" t="n">
-        <v>1086.52</v>
-      </c>
-      <c r="AF37" s="31" t="n">
-        <v>1011.959</v>
-      </c>
-      <c r="AG37" s="31" t="n">
-        <v>-4.57</v>
-      </c>
-      <c r="AH37" s="31" t="n">
-        <v>1150.4376</v>
-      </c>
-      <c r="AI37" s="31" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="AJ37" s="31" t="n">
-        <v>1230.968232</v>
-      </c>
-      <c r="AK37" s="31" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="AL37" s="31" t="n">
-        <v>1060.38</v>
-      </c>
-      <c r="AM37" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="31" t="n"/>
-      <c r="AP37" s="31" t="n"/>
-      <c r="AQ37" s="31" t="n"/>
-      <c r="AR37" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS37" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT37" s="31" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="AU37" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV37" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW37" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX37" s="31" t="n"/>
-      <c r="AY37" s="31" t="inlineStr"/>
-      <c r="AZ37" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA37" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB37" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC37" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD37" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE37" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 1011.96</t>
-        </is>
-      </c>
-      <c r="BF37" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG37" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-MMM-20260810-0649c0</t>
-        </is>
-      </c>
-      <c r="B38" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C38" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D38" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E38" s="31" t="inlineStr">
-        <is>
-          <t>MMM</t>
-        </is>
-      </c>
-      <c r="F38" s="31" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="G38" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="31" t="n"/>
-      <c r="J38" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="K38" s="31" t="n"/>
-      <c r="L38" s="31" t="n"/>
-      <c r="M38" s="31" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="N38" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O38" s="31" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P38" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q38" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R38" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S38" s="31" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T38" s="31" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U38" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V38" s="31" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="W38" s="31" t="n"/>
-      <c r="X38" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z38" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA38" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB38" s="31" t="n">
-        <v>182.08</v>
-      </c>
-      <c r="AC38" s="31" t="n">
-        <v>182.0800018310547</v>
-      </c>
-      <c r="AD38" s="31" t="n">
-        <v>156.64</v>
-      </c>
-      <c r="AE38" s="31" t="n">
-        <v>163.04</v>
-      </c>
-      <c r="AF38" s="31" t="n">
-        <v>151.848</v>
-      </c>
-      <c r="AG38" s="31" t="n">
-        <v>-16.6</v>
-      </c>
-      <c r="AH38" s="31" t="n">
-        <v>172.6272</v>
-      </c>
-      <c r="AI38" s="31" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="AJ38" s="31" t="n">
-        <v>184.711104</v>
-      </c>
-      <c r="AK38" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL38" s="31" t="n">
-        <v>182.08</v>
-      </c>
-      <c r="AM38" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="31" t="n"/>
-      <c r="AP38" s="31" t="n"/>
-      <c r="AQ38" s="31" t="n"/>
-      <c r="AR38" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS38" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT38" s="31" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="AU38" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV38" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW38" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX38" s="31" t="n"/>
-      <c r="AY38" s="31" t="inlineStr"/>
-      <c r="AZ38" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA38" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB38" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC38" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD38" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE38" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 151.85</t>
-        </is>
-      </c>
-      <c r="BF38" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG38" s="31" t="inlineStr">
+      <c r="BG18" s="31" t="inlineStr">
         <is>
           <t>🟡 Normal window · 10:00-14:30 IST</t>
         </is>
@@ -40112,7 +35954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40207,50 +36049,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RETIRED_DORMANT</t>
+          <t>ACTIVE_PRODUCTION</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>R1 formally retired per configs/aegis_retirement.yaml · DORMANT_BY_DESIGN · historical records preserved</t>
+          <t>runner produced signals and/or opened positions in window</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>508</v>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>508</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>502</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>5.66</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-3.45</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (n=0 · minimum 30 for stable statistics)</t>
+          <t>INSUFFICIENT (n=9 · minimum 30 for stable statistics)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -40262,104 +36100,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>COMBINED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACTIVE_PRODUCTION</t>
+          <t>PIPELINE_FAILURE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>runner produced signals and/or opened positions in window</t>
+          <t>0 signals AND 0 opened positions in window AND no recent engine activity in aegis_daily_v2_history · investigate engine health</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-3.45</v>
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (n=9 · minimum 30 for stable statistics)</t>
+          <t>INSUFFICIENT (n=0 · minimum 30 for stable statistics)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
-        <is>
-          <t>canonical:runner_accountability</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>COMBINED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PIPELINE_FAILURE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0 signals AND 0 opened positions in window AND no recent engine activity in aegis_daily_v2_history · investigate engine health</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=0 · minimum 30 for stable statistics)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>canonical:runner_accountability</t>
         </is>

--- a/reports/telegram/aegis_usa_2026-09-01.xlsx
+++ b/reports/telegram/aegis_usa_2026-09-01.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -489,9 +489,11 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -551,17 +553,27 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>Dynamic Stop</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Engine Verdict</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Would-Have-Exited-On</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>As-Of</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Provenance</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -598,19 +610,27 @@
       <c r="H5" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="n">
+        <v>64.02290000000001</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -647,19 +667,27 @@
       <c r="H6" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="n">
+        <v>85.8629</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -696,19 +724,27 @@
       <c r="H7" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="n">
+        <v>161.7654</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -745,19 +781,27 @@
       <c r="H8" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="n">
+        <v>156.903</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -794,19 +838,27 @@
       <c r="H9" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="n">
+        <v>352.7764</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -843,19 +895,27 @@
       <c r="H10" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="n">
+        <v>343.9312</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>HOLD (audit-only)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>canonical:Registry+prices</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>held</t>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>canonical:Registry+prices+dynamic_exit_bridge</t>
         </is>
       </c>
     </row>
@@ -887,14 +947,38 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Dynamic Stop = today's stop level from the coded exit engine (dynamic_risk_v2 ATR-based, else recommendation entry_zone.stop_loss, else entry × 0.94).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Engine Verdict = what the coded lifecycle engine (evaluate_position) says today. HOLD if no trigger. EXIT_STOP / EXIT_TARGET / EXIT_HORIZON if triggered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Would-Have-Exited-On = if the engine says exit today, this is the first date the position crossed the trigger. Positions are NOT retroactively closed in the current release · this is audit-only until the wiring is enforced.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="9">
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
